--- a/output/pdf_financials_xlsx/MBO.xlsx
+++ b/output/pdf_financials_xlsx/MBO.xlsx
@@ -4166,31 +4166,31 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.13765</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.13765</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.145108</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.600275</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.043869</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.95272</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.012945</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.9264869999999999</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.6221</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0.38528</v>
@@ -9319,7 +9319,11 @@
           <t>Warrant reserves 10</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -9457,7 +9461,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -10585,7 +10593,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -10723,7 +10735,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -11498,7 +11514,11 @@
           <t>Warrant reserve 13</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -11638,7 +11658,11 @@
           <t>Share-based payments reserve 13</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -12348,7 +12372,11 @@
           <t>Warrant reserve 13</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -12488,7 +12516,11 @@
           <t>Share-based payment reserves 13</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -13561,7 +13593,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" s="5" t="n">
         <v>0.022335</v>
       </c>
@@ -13628,7 +13664,11 @@
           <t>Share-based payments reserve 10</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" s="5" t="n">
         <v>0.115315</v>
       </c>

--- a/output/pdf_financials_xlsx/MBO.xlsx
+++ b/output/pdf_financials_xlsx/MBO.xlsx
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.178216</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.217834</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>5.004685</v>
@@ -810,10 +810,10 @@
         <v>0.28027</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>2.514422</v>
+        <v>6.492842</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>2.257699</v>
+        <v>5.729803</v>
       </c>
     </row>
     <row r="11">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.061584</v>
+        <v>-0.116632</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.015891</v>
+        <v>-0.201943</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-4.399119</v>
@@ -852,10 +852,10 @@
         <v>-0.273349</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>3.706213</v>
+        <v>-0.272207</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>3.34605</v>
+        <v>-0.126054</v>
       </c>
     </row>
     <row r="12">
@@ -888,7 +888,7 @@
         <v>-0.037129</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000115</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>-0.798509</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.192848</v>
+        <v>-0.192733</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-1.465016</v>
@@ -1644,7 +1644,7 @@
         <v>-0.793764</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.192848</v>
+        <v>-0.192733</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-1.465016</v>
@@ -1686,7 +1686,7 @@
         <v>-1735.762081784387</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-4096.176720475786</v>
+        <v>-4093.734069668649</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>-21167.69252998121</v>
@@ -1796,37 +1796,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.011385</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.015873</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001546</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.441967</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.118305</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.07688300000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.30719</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.05107</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.017708</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.746783</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.28439</v>
       </c>
     </row>
     <row r="35">
@@ -1876,37 +1876,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.011385</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.015873</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001546</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.441967</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.118305</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.07688300000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.30719</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.05107</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.017708</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.746783</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.28439</v>
       </c>
     </row>
     <row r="37">
@@ -2356,37 +2356,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.0162</v>
+        <v>0.004815</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.020665</v>
+        <v>0.004792</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.001546</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.477721</v>
+        <v>0.035754</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.158047</v>
+        <v>0.039742</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.122369</v>
+        <v>0.045486</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.376844</v>
+        <v>0.06965399999999999</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.065479</v>
+        <v>0.014409</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.031421</v>
+        <v>0.013713</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.82951</v>
+        <v>0.08272699999999999</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.478526</v>
+        <v>0.194136</v>
       </c>
     </row>
     <row r="49">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
@@ -25046,7 +25046,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -25188,7 +25188,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -28126,7 +28126,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -28201,7 +28201,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">

--- a/output/pdf_financials_xlsx/MBO.xlsx
+++ b/output/pdf_financials_xlsx/MBO.xlsx
@@ -1590,10 +1590,10 @@
         <v>0.001575</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2.173715</v>
+        <v>2.171128</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.929967</v>
+        <v>0.927821</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.00183</v>
@@ -1632,10 +1632,10 @@
         <v>-0.160652</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.96015</v>
+        <v>-2.962737</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.005568</v>
+        <v>-1.007714</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.892846</v>
@@ -1674,10 +1674,10 @@
         <v>-356.8616997645386</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-488.8236790044355</v>
+        <v>-489.2508826453269</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-340.1970336689401</v>
+        <v>-340.9230540218686</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-1253.997191011236</v>
@@ -4466,10 +4466,10 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>2.171128</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.927821</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -30678,7 +30678,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -32737,7 +32737,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">

--- a/output/pdf_financials_xlsx/MBO.xlsx
+++ b/output/pdf_financials_xlsx/MBO.xlsx
@@ -1264,7 +1264,7 @@
         <v>-0.835638</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0.192848</v>
+        <v>-0.243707</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-1.465016</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-0.050859</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
@@ -3147,28 +3147,28 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.088421</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.173082</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.288032</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.135685</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.123366</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.216151</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.336458</v>
       </c>
     </row>
     <row r="68">
@@ -3187,16 +3187,16 @@
         <v>0.279081</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>0.088421</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>0.173082</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>0.288032</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I68" s="3" t="n">
         <v>0.181162</v>
@@ -3205,10 +3205,10 @@
         <v>0.162007</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>1.55502</v>
+        <v>1.771171</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>2.162217</v>
+        <v>2.498675</v>
       </c>
     </row>
     <row r="69">
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.564558</v>
+        <v>0.276526</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>0</v>
@@ -3485,10 +3485,10 @@
         <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.392407</v>
+        <v>0.176256</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.397786</v>
+        <v>0.061328</v>
       </c>
     </row>
     <row r="76">
@@ -4433,10 +4433,10 @@
         <v>-0.951793</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>-0.835638</v>
+        <v>-0.553315</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-0.192848</v>
+        <v>-0.243707</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-1.465016</v>
@@ -4778,10 +4778,10 @@
         <v>0</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>0.059196</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>0.023531</v>
       </c>
     </row>
     <row r="108">
@@ -14305,7 +14305,11 @@
           <t>Share based payment expense</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -15423,7 +15427,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -16324,7 +16332,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -18288,7 +18300,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -28771,7 +28787,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -28840,7 +28860,11 @@
           <t>Net loss from discontinued operations 17</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -28877,7 +28901,7 @@
         </is>
       </c>
       <c r="L325" s="5" t="n">
-        <v>0.050859</v>
+        <v>-0.050859</v>
       </c>
       <c r="M325" t="inlineStr">
         <is>
@@ -33449,7 +33473,11 @@
           <t>Income tax recovery 6,18</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
